--- a/tams-invest-parent/tams-invest-portfolio/src/main/resources/tpl/PtlCashFlow001.xlsx
+++ b/tams-invest-parent/tams-invest-portfolio/src/main/resources/tpl/PtlCashFlow001.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>业务编号</t>
   </si>
@@ -53,6 +53,10 @@
   </si>
   <si>
     <t>交易对手</t>
+  </si>
+  <si>
+    <t>有效状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -107,12 +111,15 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -154,7 +161,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -189,7 +196,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -398,61 +405,64 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="17.875" customWidth="1"/>
-    <col min="3" max="3" width="16.375" customWidth="1"/>
-    <col min="4" max="5" width="17.5" customWidth="1"/>
-    <col min="6" max="6" width="17.25" customWidth="1"/>
-    <col min="7" max="7" width="19.25" customWidth="1"/>
-    <col min="8" max="8" width="18.25" customWidth="1"/>
-    <col min="9" max="9" width="15.25" customWidth="1"/>
-    <col min="10" max="10" width="14.625" customWidth="1"/>
-    <col min="11" max="11" width="12.625" customWidth="1"/>
-    <col min="12" max="12" width="16.125" customWidth="1"/>
-    <col min="13" max="13" width="17.25" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="17.875" customWidth="1"/>
+    <col min="4" max="4" width="16.375" customWidth="1"/>
+    <col min="5" max="6" width="17.5" customWidth="1"/>
+    <col min="7" max="7" width="17.25" customWidth="1"/>
+    <col min="8" max="8" width="19.25" customWidth="1"/>
+    <col min="9" max="9" width="18.25" customWidth="1"/>
+    <col min="10" max="10" width="15.25" customWidth="1"/>
+    <col min="11" max="11" width="14.625" customWidth="1"/>
+    <col min="12" max="12" width="12.625" customWidth="1"/>
+    <col min="13" max="13" width="16.125" customWidth="1"/>
+    <col min="14" max="14" width="17.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
     </row>

--- a/tams-invest-parent/tams-invest-portfolio/src/main/resources/tpl/PtlCashFlow001.xlsx
+++ b/tams-invest-parent/tams-invest-portfolio/src/main/resources/tpl/PtlCashFlow001.xlsx
@@ -63,6 +63,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -99,8 +102,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -412,7 +416,7 @@
     <col min="3" max="3" width="17.875" customWidth="1"/>
     <col min="4" max="4" width="16.375" customWidth="1"/>
     <col min="5" max="6" width="17.5" customWidth="1"/>
-    <col min="7" max="7" width="17.25" customWidth="1"/>
+    <col min="7" max="7" width="17.25" style="1" customWidth="1"/>
     <col min="8" max="8" width="19.25" customWidth="1"/>
     <col min="9" max="9" width="18.25" customWidth="1"/>
     <col min="10" max="10" width="15.25" customWidth="1"/>
@@ -441,7 +445,7 @@
       <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="H1" t="s">
@@ -469,5 +473,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>